--- a/data/trans_dic/P16A07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,92</t>
+          <t>0,2; 1,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,39</t>
+          <t>0,94; 4,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,52</t>
+          <t>0,44; 2,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,49</t>
+          <t>1,57; 4,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,75</t>
+          <t>1,92; 6,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,39</t>
+          <t>1,15; 5,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,58</t>
+          <t>2,12; 6,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,26</t>
+          <t>3,02; 6,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,08</t>
+          <t>1,21; 3,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,13</t>
+          <t>1,3; 3,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,08</t>
+          <t>1,45; 3,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,66</t>
+          <t>2,56; 4,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,48</t>
+          <t>0,58; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,58</t>
+          <t>1,57; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,08</t>
+          <t>0,52; 2,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,82</t>
+          <t>1,68; 4,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,32</t>
+          <t>4,07; 9,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,07</t>
+          <t>2,37; 7,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,5</t>
+          <t>1,33; 5,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,94</t>
+          <t>4,27; 8,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,71</t>
+          <t>2,75; 5,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,65</t>
+          <t>2,21; 5,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,44</t>
+          <t>1,21; 3,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,53</t>
+          <t>3,1; 5,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,3</t>
+          <t>1,31; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,31</t>
+          <t>2,81; 6,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,78</t>
+          <t>1,62; 4,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,67</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,98</t>
+          <t>4,08; 12,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 14,4</t>
+          <t>6,7; 14,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 16,97</t>
+          <t>6,54; 16,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 13,11</t>
+          <t>6,56; 13,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,36</t>
+          <t>2,41; 5,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,84</t>
+          <t>4,49; 7,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,81</t>
+          <t>3,41; 7,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,9</t>
+          <t>1,96; 6,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,94</t>
+          <t>1,38; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,03</t>
+          <t>2,67; 5,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,53</t>
+          <t>1,68; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,97</t>
+          <t>2,7; 4,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,11</t>
+          <t>4,58; 8,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,73</t>
+          <t>5,83; 9,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,1</t>
+          <t>3,78; 7,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,59</t>
+          <t>3,24; 8,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,49</t>
+          <t>2,77; 4,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,34</t>
+          <t>4,22; 6,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,69</t>
+          <t>2,82; 4,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,08</t>
+          <t>3,37; 5,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,16</t>
+          <t>2,0; 5,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,16</t>
+          <t>1,35; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,25</t>
+          <t>1,6; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,24</t>
+          <t>2,65; 6,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,44</t>
+          <t>6,11; 10,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 15,05</t>
+          <t>10,11; 14,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,05</t>
+          <t>8,84; 13,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,02</t>
+          <t>6,81; 11,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,04</t>
+          <t>4,97; 8,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,01</t>
+          <t>7,04; 10,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,92</t>
+          <t>5,96; 8,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,74</t>
+          <t>5,93; 8,77</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,0</t>
+          <t>1,58; 6,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,8</t>
+          <t>0,33; 3,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,05</t>
+          <t>0,64; 4,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,97</t>
+          <t>5,1; 8,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,65</t>
+          <t>7,1; 10,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,48</t>
+          <t>6,22; 9,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,73</t>
+          <t>6,45; 9,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,21</t>
+          <t>4,68; 6,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,6</t>
+          <t>5,73; 8,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,7</t>
+          <t>5,17; 7,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,86</t>
+          <t>5,15; 7,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,67</t>
+          <t>1,71; 2,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,72</t>
+          <t>2,47; 3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,77</t>
+          <t>1,74; 2,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,0</t>
+          <t>2,52; 3,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,36</t>
+          <t>5,63; 7,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,32</t>
+          <t>7,47; 9,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,05</t>
+          <t>6,32; 8,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,04</t>
+          <t>5,88; 8,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,85</t>
+          <t>3,87; 4,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,34</t>
+          <t>5,24; 6,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,28</t>
+          <t>4,19; 5,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,81</t>
+          <t>4,49; 5,87</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1014; 9093</t>
+          <t>966; 9128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4168; 19197</t>
+          <t>4107; 19479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1914; 10834</t>
+          <t>1870; 10075</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8491; 22678</t>
+          <t>7952; 22498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6348; 20714</t>
+          <t>5898; 18950</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3521; 16949</t>
+          <t>3626; 17158</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7167; 22819</t>
+          <t>7374; 23463</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12910; 28029</t>
+          <t>13508; 28269</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8866; 24007</t>
+          <t>9457; 24654</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10524; 31074</t>
+          <t>9758; 29584</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11301; 31688</t>
+          <t>11257; 28821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24233; 44438</t>
+          <t>24382; 46600</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2118; 12758</t>
+          <t>2141; 13163</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6275; 23254</t>
+          <t>6529; 23984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1948; 11634</t>
+          <t>1975; 10940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7032; 21805</t>
+          <t>7582; 22391</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15290; 34662</t>
+          <t>15149; 34908</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8064; 23837</t>
+          <t>7982; 23649</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5846; 20462</t>
+          <t>4957; 19705</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15803; 30374</t>
+          <t>16341; 30725</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20173; 42159</t>
+          <t>20350; 42069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17064; 42630</t>
+          <t>16676; 40676</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8713; 25750</t>
+          <t>9070; 25497</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25895; 46132</t>
+          <t>25903; 46461</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7638; 23299</t>
+          <t>7099; 22444</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17621; 39516</t>
+          <t>17581; 39131</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8938; 24945</t>
+          <t>8460; 23916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6095; 37896</t>
+          <t>5898; 39693</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6385; 20099</t>
+          <t>6852; 21149</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17367; 37154</t>
+          <t>17285; 36376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11317; 28189</t>
+          <t>10863; 28181</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10592; 21881</t>
+          <t>10952; 22407</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17181; 38050</t>
+          <t>17137; 38502</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39101; 69346</t>
+          <t>39719; 68174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22794; 46857</t>
+          <t>23444; 48374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14651; 57623</t>
+          <t>16382; 56748</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16198; 36365</t>
+          <t>17087; 36319</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29708; 58231</t>
+          <t>30846; 57925</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19176; 40626</t>
+          <t>19333; 41759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28237; 51440</t>
+          <t>27961; 51178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32450; 57899</t>
+          <t>32725; 59407</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44648; 74624</t>
+          <t>44698; 75153</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31190; 58602</t>
+          <t>31194; 57983</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30782; 83924</t>
+          <t>31678; 84558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56016; 87596</t>
+          <t>54108; 86536</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81517; 122025</t>
+          <t>81101; 120107</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57834; 92747</t>
+          <t>55700; 89762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69997; 122360</t>
+          <t>67771; 119699</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6747; 21529</t>
+          <t>7001; 20807</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7721; 21219</t>
+          <t>6898; 20870</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9911; 26359</t>
+          <t>9907; 26640</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12181; 29537</t>
+          <t>12541; 28846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33227; 59382</t>
+          <t>34778; 60815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75383; 114264</t>
+          <t>76756; 112480</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66191; 103698</t>
+          <t>65296; 101050</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55216; 92443</t>
+          <t>57175; 94321</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43763; 73809</t>
+          <t>45611; 74004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87997; 127007</t>
+          <t>89363; 129535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79607; 121246</t>
+          <t>81029; 121228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79328; 114660</t>
+          <t>77855; 115133</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4597; 17892</t>
+          <t>4699; 18238</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4466</t>
+          <t>0; 6047</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>942; 8053</t>
+          <t>958; 9365</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1545; 12140</t>
+          <t>1534; 11890</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63763; 99579</t>
+          <t>63701; 100554</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78263; 117468</t>
+          <t>78299; 116783</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66174; 102576</t>
+          <t>67264; 103602</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49598; 73979</t>
+          <t>49001; 73651</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72617; 111600</t>
+          <t>72412; 107765</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79810; 117768</t>
+          <t>78385; 117696</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68559; 105366</t>
+          <t>70852; 107887</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51925; 78641</t>
+          <t>51512; 78870</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>55240; 87257</t>
+          <t>55957; 86841</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>86605; 126874</t>
+          <t>84375; 129616</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59043; 93699</t>
+          <t>58992; 94561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83690; 134917</t>
+          <t>84958; 131830</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>190073; 248465</t>
+          <t>190065; 248046</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>261505; 329893</t>
+          <t>264337; 328917</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>218169; 284321</t>
+          <t>223038; 284443</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>212498; 287164</t>
+          <t>209944; 286415</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>254426; 322310</t>
+          <t>256980; 325746</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>358980; 440735</t>
+          <t>363943; 445727</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289480; 364916</t>
+          <t>290015; 366580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>310369; 403333</t>
+          <t>312143; 407721</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,93</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,46</t>
+          <t>0,96; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,35</t>
+          <t>0,45; 2,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,45</t>
+          <t>1,56; 4,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,18</t>
+          <t>1,93; 6,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,46</t>
+          <t>1,2; 5,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,76</t>
+          <t>2,02; 6,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,32</t>
+          <t>3,09; 6,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,16</t>
+          <t>1,19; 3,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,94</t>
+          <t>1,4; 3,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,71</t>
+          <t>1,42; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,89</t>
+          <t>2,46; 4,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,59</t>
+          <t>0,59; 3,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,75</t>
+          <t>1,47; 5,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,9</t>
+          <t>0,5; 2,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,95</t>
+          <t>1,58; 4,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,39</t>
+          <t>4,18; 9,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,02</t>
+          <t>2,24; 6,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,29</t>
+          <t>1,52; 5,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,03</t>
+          <t>4,23; 7,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,69</t>
+          <t>2,67; 5,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,39</t>
+          <t>2,2; 5,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,4</t>
+          <t>1,21; 3,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,57</t>
+          <t>3,16; 5,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,14</t>
+          <t>1,47; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,25</t>
+          <t>2,75; 6,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,58</t>
+          <t>1,73; 4,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>2,82; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,6</t>
+          <t>3,93; 12,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,1</t>
+          <t>6,62; 14,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 16,96</t>
+          <t>6,42; 16,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,42</t>
+          <t>5,65; 12,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,42</t>
+          <t>2,6; 5,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,71</t>
+          <t>4,39; 7,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,03</t>
+          <t>3,4; 7,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,79</t>
+          <t>4,21; 7,52</t>
         </is>
       </c>
     </row>
@@ -1084,47 +1084,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,93</t>
+          <t>1,38; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,01</t>
+          <t>2,63; 5,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,63</t>
+          <t>1,67; 3,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,95</t>
+          <t>2,83; 4,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,32</t>
+          <t>4,69; 8,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,8</t>
+          <t>5,91; 9,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,02</t>
+          <t>3,95; 7,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,65</t>
+          <t>6,57; 9,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,43</t>
+          <t>2,74; 4,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,24</t>
+          <t>4,22; 6,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,54</t>
+          <t>2,86; 4,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,95</t>
+          <t>4,69; 6,61</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,95</t>
+          <t>1,83; 5,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,1</t>
+          <t>1,36; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,29</t>
+          <t>1,61; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,09</t>
+          <t>2,47; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,69</t>
+          <t>6,03; 10,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,81</t>
+          <t>10,03; 15,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,69</t>
+          <t>9,09; 13,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,24</t>
+          <t>8,54; 11,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,06</t>
+          <t>4,85; 8,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,21</t>
+          <t>7,1; 10,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,92</t>
+          <t>6,0; 8,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,77</t>
+          <t>6,31; 8,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,12</t>
+          <t>1,56; 5,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,26</t>
+          <t>0,33; 2,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,94</t>
+          <t>0,99; 6,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,05</t>
+          <t>5,17; 7,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,59</t>
+          <t>7,0; 10,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,57</t>
+          <t>5,95; 9,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,69</t>
+          <t>6,29; 9,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,97</t>
+          <t>4,71; 7,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,6</t>
+          <t>5,75; 8,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,88</t>
+          <t>5,06; 7,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,88</t>
+          <t>5,24; 7,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,66</t>
+          <t>1,71; 2,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,8</t>
+          <t>2,41; 3,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,79</t>
+          <t>1,76; 2,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,91</t>
+          <t>2,84; 4,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,34</t>
+          <t>5,65; 7,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,3</t>
+          <t>7,45; 9,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,05</t>
+          <t>6,28; 8,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,02</t>
+          <t>7,0; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,9</t>
+          <t>3,8; 4,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,41</t>
+          <t>5,21; 6,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,3</t>
+          <t>4,18; 5,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,87</t>
+          <t>5,16; 6,15</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>35759</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>966; 9128</t>
+          <t>866; 8561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4107; 19479</t>
+          <t>4193; 19553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1870; 10075</t>
+          <t>1920; 11727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7952; 22498</t>
+          <t>8588; 24882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5898; 18950</t>
+          <t>5911; 19577</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3626; 17158</t>
+          <t>3770; 17374</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7374; 23463</t>
+          <t>7008; 22761</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13508; 28269</t>
+          <t>15079; 30770</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9457; 24654</t>
+          <t>9296; 25388</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9758; 29584</t>
+          <t>10520; 29769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11257; 28821</t>
+          <t>10998; 28845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24382; 46600</t>
+          <t>25537; 47590</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>38208</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2141; 13163</t>
+          <t>2159; 12693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6529; 23984</t>
+          <t>6118; 24081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1975; 10940</t>
+          <t>1900; 10839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7582; 22391</t>
+          <t>7642; 22293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15149; 34908</t>
+          <t>15531; 34752</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7982; 23649</t>
+          <t>7535; 23096</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4957; 19705</t>
+          <t>5667; 19290</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16341; 30725</t>
+          <t>17895; 33262</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20350; 42069</t>
+          <t>19727; 41471</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16676; 40676</t>
+          <t>16581; 39890</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9070; 25497</t>
+          <t>9087; 26058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25903; 46461</t>
+          <t>28606; 51551</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36478</t>
+          <t>37996</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7099; 22444</t>
+          <t>7984; 22162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17581; 39131</t>
+          <t>17228; 39797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8460; 23916</t>
+          <t>9046; 25387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5898; 39693</t>
+          <t>13313; 32247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6852; 21149</t>
+          <t>6597; 21479</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17285; 36376</t>
+          <t>17085; 36358</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10863; 28181</t>
+          <t>10658; 27613</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10952; 22407</t>
+          <t>10601; 22728</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17137; 38502</t>
+          <t>18470; 38074</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39719; 68174</t>
+          <t>38815; 67634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23444; 48374</t>
+          <t>23371; 48999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16382; 56748</t>
+          <t>27733; 49559</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>100157</t>
+          <t>111463</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17087; 36319</t>
+          <t>17088; 36478</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30846; 57925</t>
+          <t>30412; 58127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19333; 41759</t>
+          <t>19240; 41652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27961; 51178</t>
+          <t>32002; 56243</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32725; 59407</t>
+          <t>33478; 59913</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44698; 75153</t>
+          <t>45289; 74994</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31194; 57983</t>
+          <t>32631; 58257</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31678; 84558</t>
+          <t>56538; 83972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54108; 86536</t>
+          <t>53407; 87651</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81101; 120107</t>
+          <t>81144; 121583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55700; 89762</t>
+          <t>56443; 90249</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67771; 119699</t>
+          <t>93486; 131766</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>84149</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96317</t>
+          <t>105265</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7001; 20807</t>
+          <t>6381; 20610</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6898; 20870</t>
+          <t>6951; 20909</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9907; 26640</t>
+          <t>9997; 26096</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12541; 28846</t>
+          <t>13974; 32301</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34778; 60815</t>
+          <t>34324; 61624</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76756; 112480</t>
+          <t>76155; 115094</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65296; 101050</t>
+          <t>67140; 99521</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57175; 94321</t>
+          <t>70861; 99470</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45611; 74004</t>
+          <t>44582; 74554</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89363; 129535</t>
+          <t>90076; 128974</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81029; 121228</t>
+          <t>81531; 120338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>77855; 115133</t>
+          <t>88091; 120810</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>59556</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64226</t>
+          <t>70600</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4699; 18238</t>
+          <t>4638; 17711</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6047</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>958; 9365</t>
+          <t>949; 8448</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1534; 11890</t>
+          <t>2347; 14997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63701; 100554</t>
+          <t>64573; 97497</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78299; 116783</t>
+          <t>77242; 115404</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67264; 103602</t>
+          <t>64414; 102244</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49001; 73651</t>
+          <t>53010; 77970</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72412; 107765</t>
+          <t>72855; 110035</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>78385; 117696</t>
+          <t>78700; 116357</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70852; 107887</t>
+          <t>69220; 108979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51512; 78870</t>
+          <t>56638; 85720</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>119719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>255937</t>
+          <t>279573</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>365672</t>
+          <t>399292</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>55957; 86841</t>
+          <t>55977; 88781</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84375; 129616</t>
+          <t>82389; 129228</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58992; 94561</t>
+          <t>59463; 94813</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84958; 131830</t>
+          <t>97856; 142264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>190065; 248046</t>
+          <t>190754; 246725</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>264337; 328917</t>
+          <t>263493; 329073</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>223038; 284443</t>
+          <t>221739; 283425</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>209944; 286415</t>
+          <t>254424; 304508</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>256980; 325746</t>
+          <t>252801; 321087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>363943; 445727</t>
+          <t>362278; 446803</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>290015; 366580</t>
+          <t>289185; 366007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>312143; 407721</t>
+          <t>364728; 434831</t>
         </is>
       </c>
     </row>
